--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -1417,27 +1417,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127317097</v>
+        <v>127317342</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>58027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103008</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483485</v>
+        <v>483672</v>
       </c>
       <c r="R9" t="n">
-        <v>6539403</v>
+        <v>6539402</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,27 +1523,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127317342</v>
+        <v>127317097</v>
       </c>
       <c r="B10" t="n">
-        <v>58027</v>
+        <v>57987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483672</v>
+        <v>483485</v>
       </c>
       <c r="R10" t="n">
-        <v>6539402</v>
+        <v>6539403</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127317455</v>
+        <v>127317157</v>
       </c>
       <c r="B4" t="n">
-        <v>58162</v>
+        <v>57817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102995</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483713</v>
+        <v>483488</v>
       </c>
       <c r="R4" t="n">
-        <v>6539472</v>
+        <v>6539383</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127317157</v>
+        <v>127317455</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>58162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483488</v>
+        <v>483713</v>
       </c>
       <c r="R5" t="n">
-        <v>6539383</v>
+        <v>6539472</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127317157</v>
+        <v>127317455</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>58162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483488</v>
+        <v>483713</v>
       </c>
       <c r="R4" t="n">
-        <v>6539383</v>
+        <v>6539472</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127317455</v>
+        <v>127317157</v>
       </c>
       <c r="B5" t="n">
-        <v>58162</v>
+        <v>57817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102995</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483713</v>
+        <v>483488</v>
       </c>
       <c r="R5" t="n">
-        <v>6539472</v>
+        <v>6539383</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127317455</v>
+        <v>127317157</v>
       </c>
       <c r="B4" t="n">
-        <v>58162</v>
+        <v>57817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102995</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483713</v>
+        <v>483488</v>
       </c>
       <c r="R4" t="n">
-        <v>6539472</v>
+        <v>6539383</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127317157</v>
+        <v>127317455</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>58162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483488</v>
+        <v>483713</v>
       </c>
       <c r="R5" t="n">
-        <v>6539383</v>
+        <v>6539472</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1417,27 +1417,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127317342</v>
+        <v>127317097</v>
       </c>
       <c r="B9" t="n">
-        <v>58027</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483672</v>
+        <v>483485</v>
       </c>
       <c r="R9" t="n">
-        <v>6539402</v>
+        <v>6539403</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,27 +1523,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127317097</v>
+        <v>127317342</v>
       </c>
       <c r="B10" t="n">
-        <v>57987</v>
+        <v>58027</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103008</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483485</v>
+        <v>483672</v>
       </c>
       <c r="R10" t="n">
-        <v>6539403</v>
+        <v>6539402</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127317351</v>
       </c>
       <c r="B2" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127317214</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127317157</v>
+        <v>127317455</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>58166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483488</v>
+        <v>483713</v>
       </c>
       <c r="R4" t="n">
-        <v>6539383</v>
+        <v>6539472</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127317455</v>
+        <v>127317157</v>
       </c>
       <c r="B5" t="n">
-        <v>58162</v>
+        <v>57821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102995</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483713</v>
+        <v>483488</v>
       </c>
       <c r="R5" t="n">
-        <v>6539472</v>
+        <v>6539383</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,7 +1102,7 @@
         <v>127317094</v>
       </c>
       <c r="B6" t="n">
-        <v>57987</v>
+        <v>57991</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127317432</v>
       </c>
       <c r="B7" t="n">
-        <v>58334</v>
+        <v>58338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>127317155</v>
       </c>
       <c r="B8" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>127317097</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57991</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>127317342</v>
       </c>
       <c r="B10" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -1417,27 +1417,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127317097</v>
+        <v>127317342</v>
       </c>
       <c r="B9" t="n">
-        <v>57991</v>
+        <v>58031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103008</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483485</v>
+        <v>483672</v>
       </c>
       <c r="R9" t="n">
-        <v>6539403</v>
+        <v>6539402</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,27 +1523,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127317342</v>
+        <v>127317097</v>
       </c>
       <c r="B10" t="n">
-        <v>58031</v>
+        <v>57991</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483672</v>
+        <v>483485</v>
       </c>
       <c r="R10" t="n">
-        <v>6539402</v>
+        <v>6539403</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -1417,27 +1417,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127317342</v>
+        <v>127317097</v>
       </c>
       <c r="B9" t="n">
-        <v>58031</v>
+        <v>57991</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483672</v>
+        <v>483485</v>
       </c>
       <c r="R9" t="n">
-        <v>6539402</v>
+        <v>6539403</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,27 +1523,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127317097</v>
+        <v>127317342</v>
       </c>
       <c r="B10" t="n">
-        <v>57991</v>
+        <v>58031</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103008</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483485</v>
+        <v>483672</v>
       </c>
       <c r="R10" t="n">
-        <v>6539403</v>
+        <v>6539402</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127317351</v>
       </c>
       <c r="B2" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127317214</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127317455</v>
+        <v>127317157</v>
       </c>
       <c r="B4" t="n">
-        <v>58166</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102995</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483713</v>
+        <v>483488</v>
       </c>
       <c r="R4" t="n">
-        <v>6539472</v>
+        <v>6539383</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127317157</v>
+        <v>127317455</v>
       </c>
       <c r="B5" t="n">
-        <v>57821</v>
+        <v>58168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483488</v>
+        <v>483713</v>
       </c>
       <c r="R5" t="n">
-        <v>6539383</v>
+        <v>6539472</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,7 +1102,7 @@
         <v>127317094</v>
       </c>
       <c r="B6" t="n">
-        <v>57991</v>
+        <v>57993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127317432</v>
       </c>
       <c r="B7" t="n">
-        <v>58338</v>
+        <v>58340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>127317155</v>
       </c>
       <c r="B8" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>127317097</v>
       </c>
       <c r="B9" t="n">
-        <v>57991</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>127317342</v>
       </c>
       <c r="B10" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127317157</v>
+        <v>127317455</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>58168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483488</v>
+        <v>483713</v>
       </c>
       <c r="R4" t="n">
-        <v>6539383</v>
+        <v>6539472</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127317455</v>
+        <v>127317157</v>
       </c>
       <c r="B5" t="n">
-        <v>58168</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102995</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483713</v>
+        <v>483488</v>
       </c>
       <c r="R5" t="n">
-        <v>6539472</v>
+        <v>6539383</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1417,27 +1417,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127317097</v>
+        <v>127317342</v>
       </c>
       <c r="B9" t="n">
-        <v>57993</v>
+        <v>58033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103008</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483485</v>
+        <v>483672</v>
       </c>
       <c r="R9" t="n">
-        <v>6539403</v>
+        <v>6539402</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,27 +1523,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127317342</v>
+        <v>127317097</v>
       </c>
       <c r="B10" t="n">
-        <v>58033</v>
+        <v>57993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483672</v>
+        <v>483485</v>
       </c>
       <c r="R10" t="n">
-        <v>6539402</v>
+        <v>6539403</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127317455</v>
+        <v>127317157</v>
       </c>
       <c r="B4" t="n">
-        <v>58168</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102995</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483713</v>
+        <v>483488</v>
       </c>
       <c r="R4" t="n">
-        <v>6539472</v>
+        <v>6539383</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127317157</v>
+        <v>127317455</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>58168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483488</v>
+        <v>483713</v>
       </c>
       <c r="R5" t="n">
-        <v>6539383</v>
+        <v>6539472</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127317157</v>
+        <v>127317455</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>58168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483488</v>
+        <v>483713</v>
       </c>
       <c r="R4" t="n">
-        <v>6539383</v>
+        <v>6539472</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127317455</v>
+        <v>127317157</v>
       </c>
       <c r="B5" t="n">
-        <v>58168</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102995</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483713</v>
+        <v>483488</v>
       </c>
       <c r="R5" t="n">
-        <v>6539472</v>
+        <v>6539383</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1417,27 +1417,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127317342</v>
+        <v>127317097</v>
       </c>
       <c r="B9" t="n">
-        <v>58033</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483672</v>
+        <v>483485</v>
       </c>
       <c r="R9" t="n">
-        <v>6539402</v>
+        <v>6539403</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,27 +1523,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127317097</v>
+        <v>127317342</v>
       </c>
       <c r="B10" t="n">
-        <v>57993</v>
+        <v>58033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103008</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483485</v>
+        <v>483672</v>
       </c>
       <c r="R10" t="n">
-        <v>6539403</v>
+        <v>6539402</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127317351</v>
       </c>
       <c r="B2" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127317214</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127317455</v>
+        <v>127317157</v>
       </c>
       <c r="B4" t="n">
-        <v>58168</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102995</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483713</v>
+        <v>483488</v>
       </c>
       <c r="R4" t="n">
-        <v>6539472</v>
+        <v>6539383</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127317157</v>
+        <v>127317455</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>58171</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483488</v>
+        <v>483713</v>
       </c>
       <c r="R5" t="n">
-        <v>6539383</v>
+        <v>6539472</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,7 +1102,7 @@
         <v>127317094</v>
       </c>
       <c r="B6" t="n">
-        <v>57993</v>
+        <v>57996</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127317432</v>
       </c>
       <c r="B7" t="n">
-        <v>58340</v>
+        <v>58343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>127317155</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,27 +1417,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127317097</v>
+        <v>127317342</v>
       </c>
       <c r="B9" t="n">
-        <v>57993</v>
+        <v>58036</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103008</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483485</v>
+        <v>483672</v>
       </c>
       <c r="R9" t="n">
-        <v>6539403</v>
+        <v>6539402</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,27 +1523,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127317342</v>
+        <v>127317097</v>
       </c>
       <c r="B10" t="n">
-        <v>58033</v>
+        <v>57996</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483672</v>
+        <v>483485</v>
       </c>
       <c r="R10" t="n">
-        <v>6539402</v>
+        <v>6539403</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127317351</v>
       </c>
       <c r="B2" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127317214</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127317157</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127317455</v>
       </c>
       <c r="B5" t="n">
-        <v>58171</v>
+        <v>58177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>127317094</v>
       </c>
       <c r="B6" t="n">
-        <v>57996</v>
+        <v>58002</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127317432</v>
       </c>
       <c r="B7" t="n">
-        <v>58343</v>
+        <v>58349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>127317155</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,27 +1417,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127317342</v>
+        <v>127317097</v>
       </c>
       <c r="B9" t="n">
-        <v>58036</v>
+        <v>58002</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483672</v>
+        <v>483485</v>
       </c>
       <c r="R9" t="n">
-        <v>6539402</v>
+        <v>6539403</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,27 +1523,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127317097</v>
+        <v>127317342</v>
       </c>
       <c r="B10" t="n">
-        <v>57996</v>
+        <v>58042</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103008</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483485</v>
+        <v>483672</v>
       </c>
       <c r="R10" t="n">
-        <v>6539403</v>
+        <v>6539402</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127317157</v>
+        <v>127317455</v>
       </c>
       <c r="B4" t="n">
-        <v>57832</v>
+        <v>58177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483488</v>
+        <v>483713</v>
       </c>
       <c r="R4" t="n">
-        <v>6539383</v>
+        <v>6539472</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127317455</v>
+        <v>127317157</v>
       </c>
       <c r="B5" t="n">
-        <v>58177</v>
+        <v>57832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102995</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483713</v>
+        <v>483488</v>
       </c>
       <c r="R5" t="n">
-        <v>6539472</v>
+        <v>6539383</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127317455</v>
+        <v>127317157</v>
       </c>
       <c r="B4" t="n">
-        <v>58177</v>
+        <v>57832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102995</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483713</v>
+        <v>483488</v>
       </c>
       <c r="R4" t="n">
-        <v>6539472</v>
+        <v>6539383</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127317157</v>
+        <v>127317455</v>
       </c>
       <c r="B5" t="n">
-        <v>57832</v>
+        <v>58177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483488</v>
+        <v>483713</v>
       </c>
       <c r="R5" t="n">
-        <v>6539383</v>
+        <v>6539472</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1417,27 +1417,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127317097</v>
+        <v>127317342</v>
       </c>
       <c r="B9" t="n">
-        <v>58002</v>
+        <v>58042</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103008</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483485</v>
+        <v>483672</v>
       </c>
       <c r="R9" t="n">
-        <v>6539403</v>
+        <v>6539402</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,27 +1523,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127317342</v>
+        <v>127317097</v>
       </c>
       <c r="B10" t="n">
-        <v>58042</v>
+        <v>58002</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483672</v>
+        <v>483485</v>
       </c>
       <c r="R10" t="n">
-        <v>6539402</v>
+        <v>6539403</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1627,6 +1627,107 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130061567</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sågen, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>483723</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6539426</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -1632,7 +1632,7 @@
         <v>130061567</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127317351</v>
+        <v>127317214</v>
       </c>
       <c r="B2" t="n">
-        <v>58042</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483575</v>
+        <v>483698</v>
       </c>
       <c r="R2" t="n">
-        <v>6539399</v>
+        <v>6539409</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,57 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127317214</v>
+        <v>130061541</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>4775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sågen. Laxå, Nrk</t>
+          <t>Sågen, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483698</v>
+        <v>483608</v>
       </c>
       <c r="R3" t="n">
-        <v>6539409</v>
+        <v>6539394</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,44 +866,48 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Väg och Miljö AB, Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127317157</v>
+        <v>127317455</v>
       </c>
       <c r="B4" t="n">
-        <v>57832</v>
+        <v>58463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -922,7 +917,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483488</v>
+        <v>483713</v>
       </c>
       <c r="R4" t="n">
-        <v>6539383</v>
+        <v>6539472</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,27 +988,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127317455</v>
+        <v>127317094</v>
       </c>
       <c r="B5" t="n">
-        <v>58177</v>
+        <v>58286</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102995</v>
+        <v>103008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1037,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483713</v>
+        <v>483524</v>
       </c>
       <c r="R5" t="n">
-        <v>6539472</v>
+        <v>6539409</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,14 +1094,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127317094</v>
+        <v>127317097</v>
       </c>
       <c r="B6" t="n">
-        <v>58002</v>
+        <v>58286</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483524</v>
+        <v>483485</v>
       </c>
       <c r="R6" t="n">
-        <v>6539409</v>
+        <v>6539403</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1173,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127317432</v>
+        <v>127317342</v>
       </c>
       <c r="B7" t="n">
-        <v>58349</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,16 +1211,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1240,7 +1235,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1249,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483693</v>
+        <v>483672</v>
       </c>
       <c r="R7" t="n">
-        <v>6539403</v>
+        <v>6539402</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1279,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,32 +1306,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127317155</v>
+        <v>127317351</v>
       </c>
       <c r="B8" t="n">
-        <v>57832</v>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1346,7 +1341,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1355,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483503</v>
+        <v>483575</v>
       </c>
       <c r="R8" t="n">
-        <v>6539394</v>
+        <v>6539399</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1385,12 +1380,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,32 +1412,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127317342</v>
+        <v>127317155</v>
       </c>
       <c r="B9" t="n">
-        <v>58042</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1452,7 +1447,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1461,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483672</v>
+        <v>483503</v>
       </c>
       <c r="R9" t="n">
-        <v>6539402</v>
+        <v>6539394</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127317097</v>
+        <v>127317157</v>
       </c>
       <c r="B10" t="n">
-        <v>58002</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1529,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103008</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1558,7 +1553,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1567,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483485</v>
+        <v>483488</v>
       </c>
       <c r="R10" t="n">
-        <v>6539403</v>
+        <v>6539383</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1597,12 +1592,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,7 +1627,7 @@
         <v>130061567</v>
       </c>
       <c r="B11" t="n">
-        <v>57985</v>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,6 +1718,213 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127317432</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sågen. Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>483693</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6539403</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130061553</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sågen, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>483548</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6539377</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 59606-2023 artfynd.xlsx
+++ b/artfynd/A 59606-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127317214</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130061541</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127317455</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127317094</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127317097</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127317342</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127317351</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127317155</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1621,6 +1666,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127317157</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
           <t>Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130061567</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1828,6 +1883,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127317432</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1929,8 +1989,27 @@
           <t>Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130061553</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>